--- a/public/CinaTech_Client_Onboarding_Template.xlsx
+++ b/public/CinaTech_Client_Onboarding_Template.xlsx
@@ -1,58 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Client Onboarding" sheetId="1" r:id="rId1"/>
+    <sheet name="Client Onboarding" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;Responses Completed: &quot;0&quot; / 23&quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="8">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A1A2E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A1A2E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A1A2E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A1A2E"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2D45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4A7A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +115,166 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00155724"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00856404"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF3CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00721C24"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8D7DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +353,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +387,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +421,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,125 +556,614 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F2D45"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Field</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Your Response</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1. Client / Brand Name</v>
-      </c>
-      <c r="B2" t="str">
-        <v>[Enter name here]</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2. Industry / Niche</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[Enter industry here]</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3. Target Audience</v>
-      </c>
-      <c r="B4" t="str">
-        <v>[Enter primary demographics here]</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4. Current Core Challenges</v>
-      </c>
-      <c r="B5" t="str">
-        <v>[Enter main problems they face]</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5. Main Competitors</v>
-      </c>
-      <c r="B6" t="str">
-        <v>[Enter 2-5 competitors]</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6. Core Value Proposition / Messaging</v>
-      </c>
-      <c r="B7" t="str">
-        <v>[Enter how they pitch their product today]</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>7. Specific Goals for this Quarter/Year</v>
-      </c>
-      <c r="B8" t="str">
-        <v>[Enter the objectives they explicitly shared]</v>
-      </c>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CinaTech  —  Strategic Client Onboarding Questionnaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SUBMISSION COMPLETENESS</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Complete all 23 questions before submitting. The score below updates automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="4">
+        <f>IF(B6&lt;&gt;"",IF(LEFT(B6,1)&lt;&gt;"[",1,0),0)+IF(B7&lt;&gt;"",IF(LEFT(B7,1)&lt;&gt;"[",1,0),0)+IF(B8&lt;&gt;"",IF(LEFT(B8,1)&lt;&gt;"[",1,0),0)+IF(B11&lt;&gt;"",IF(LEFT(B11,1)&lt;&gt;"[",1,0),0)+IF(B12&lt;&gt;"",IF(LEFT(B12,1)&lt;&gt;"[",1,0),0)+IF(B13&lt;&gt;"",IF(LEFT(B13,1)&lt;&gt;"[",1,0),0)+IF(B16&lt;&gt;"",IF(LEFT(B16,1)&lt;&gt;"[",1,0),0)+IF(B17&lt;&gt;"",IF(LEFT(B17,1)&lt;&gt;"[",1,0),0)+IF(B18&lt;&gt;"",IF(LEFT(B18,1)&lt;&gt;"[",1,0),0)+IF(B21&lt;&gt;"",IF(LEFT(B21,1)&lt;&gt;"[",1,0),0)+IF(B22&lt;&gt;"",IF(LEFT(B22,1)&lt;&gt;"[",1,0),0)+IF(B25&lt;&gt;"",IF(LEFT(B25,1)&lt;&gt;"[",1,0),0)+IF(B26&lt;&gt;"",IF(LEFT(B26,1)&lt;&gt;"[",1,0),0)+IF(B29&lt;&gt;"",IF(LEFT(B29,1)&lt;&gt;"[",1,0),0)+IF(B30&lt;&gt;"",IF(LEFT(B30,1)&lt;&gt;"[",1,0),0)+IF(B31&lt;&gt;"",IF(LEFT(B31,1)&lt;&gt;"[",1,0),0)+IF(B34&lt;&gt;"",IF(LEFT(B34,1)&lt;&gt;"[",1,0),0)+IF(B35&lt;&gt;"",IF(LEFT(B35,1)&lt;&gt;"[",1,0),0)+IF(B36&lt;&gt;"",IF(LEFT(B36,1)&lt;&gt;"[",1,0),0)+IF(B39&lt;&gt;"",IF(LEFT(B39,1)&lt;&gt;"[",1,0),0)+IF(B40&lt;&gt;"",IF(LEFT(B40,1)&lt;&gt;"[",1,0),0)+IF(B43&lt;&gt;"",IF(LEFT(B43,1)&lt;&gt;"[",1,0),0)+IF(B44&lt;&gt;"",IF(LEFT(B44,1)&lt;&gt;"[",1,0),0)</f>
+        <v/>
+      </c>
+      <c r="C3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 1  —  COMPETITIVE POSITIONING AND DIFFERENTIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>P1 Q1 — Competitors
+Who are your top 3 competitors and how do clients typically compare you to them?</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>[List competitors and how prospects compare you to them]</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Name them directly. Note how prospects frame the comparison — price, quality, specialisation, speed, or reputation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>P1 Q2 — Differentiation
+What is your primary point of differentiation? (price, quality, specialisation, speed, or results guarantee)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>[Describe your primary differentiator and why clients choose you]</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Choose one main differentiator and explain it briefly. What would a client say if asked why they chose you over a competitor?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>P1 Q3 — Competitor gaps
+What do competitors offer that you currently do not?</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>[List gaps honestly — services, reach, pricing, technology, etc.]</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Be honest. This is not a weakness to hide — it is intelligence the agency needs to give you accurate strategic advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="10" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 2  —  TARGET MARKET DEFINITION AND IDEAL CLIENT PROFILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>P2 Q1 — Ideal client
+Describe your ideal client — industry, company size, geography, and decision-maker role.</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>[Industry / company size / geography / decision-maker role]</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Be specific. 'SMEs in the UK' is not enough. Example: 'Owner-operated aesthetics clinics in England, 2–10 staff, decision-maker is the clinic owner directly.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>P2 Q2 — Core problem
+What is the single biggest problem your best clients had before working with you?</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>[The core problem your best clients had — in their own words if possible]</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>State it in the client's own words if possible. This feeds directly into the Jobs-to-be-Done analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>P2 Q3 — Profitable segments
+Which client segments are most profitable for you, and which do you want more of?</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>[Most profitable segment now / segment you want more of]</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>These may not be the same. Distinguish between your current best clients and your target best clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="10" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 3  —  CLIENT ACQUISITION AND GROWTH ENGINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>P3 Q1 — Lead sources
+What are your top 3 lead sources by volume and by revenue?</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>[Top 3 by volume / Top 3 by revenue]</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Volume and revenue rankings often differ — a referral brings fewer leads but higher value. List both rankings separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>P3 Q2 — CAC and client value
+What is your average cost to acquire a new client and your average first-year client value (£)?</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>[Average CAC £ / Average first-year client value £]</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Rough estimates are fine. Include time cost if there is no fixed ad spend. CAC and LTV are foundational to the Ansoff Matrix analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>P3 Q3 — Conversion rate
+What is your current lead-to-client conversion rate, and where do most prospects drop off?</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>[Conversion rate % / Stage where prospects most commonly drop off]</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Identify the drop-off stage: awareness, enquiry, proposal, or close. Even a rough percentage is useful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="10" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 4  —  ONBOARDING FRICTION AND OPERATIONAL READINESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>P4 Q1 — Onboarding process
+Walk us through your current client onboarding process. Where are the most common delays or friction points?</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>[Step-by-step onboarding process / friction points or common delays]</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>List each step in sequence. Mark any step that regularly causes delays, confusion, or client complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>P4 Q2 — Tools and manual steps
+What tools and systems underpin your service delivery? List any manual steps you would like to automate.</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>[Tools and systems used / manual steps you want to automate]</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Include CRM, project management, communication, billing, and reporting tools. Note any spreadsheet-based or email-based processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="10" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 5  —  PROOF OF RESULTS AND CASE STUDIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="65" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>P5 Q1 — Client outcomes
+Do you have documented client outcomes, case studies, or testimonials? Describe 1–2 specific results with numbers.</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>[Outcome 1 with numbers / Outcome 2 with numbers]</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Include percentages, revenue figures, time saved, or leads generated. Vague praise ('great results') is far less useful than specific numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="65" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>P5 Q2 — Proof in sales
+How do you currently present proof of results to prospects during the sales process?</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>[How proof is presented to prospects — format and timing]</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Examples: case study PDF, video testimonials, live results dashboard, written reference, reference call. Be specific about the format and timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="10" customHeight="1">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 6  —  SERVICE DELIVERY MODEL AND SCALABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>P6 Q1 — Delivery model
+How is your service delivered? Select from the dropdown.</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>[Select delivery model from dropdown]</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Done-for-you = you do the work. Done-with-you = collaborative. Self-serve = client uses your platform/tools. Hybrid/Mixed = combination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="65" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>P6 Q2 — Maximum capacity
+What is your maximum client capacity at current headcount, without further hiring?</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>[Maximum number of clients at current headcount]</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Estimate based on hours per client per week × available team hours. Include yourself in the calculation if you are the primary delivery resource.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>P6 Q3 — Scalability bottleneck
+What is the single biggest bottleneck to scaling your delivery?</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>[Single biggest delivery bottleneck and why]</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Be specific: is it time, a particular skill, a missing system, or capital? Identifying one root constraint is more valuable than listing several.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="10" customHeight="1">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 7  —  REVENUE MODEL AND GROWTH TRAJECTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="65" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>P7 Q1 — Revenue streams
+List your current revenue streams and the approximate percentage contribution of each.</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>[Revenue stream / % contribution — e.g. Retainer 60%, Projects 30%, Training 10%]</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Example: Retainer 60%, one-off projects 30%, training/courses 10%. If you only have one stream, note that clearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="65" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>P7 Q2 — Revenue figures
+What was your total revenue in the last 12 months, and what is your target for the next 12?</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>[Last 12 months revenue £ / Target next 12 months £]</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Exact or approximate figures in £. If revenue varies significantly month-to-month, note the range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="65" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>P7 Q3 — Recurring contracts
+Do you offer recurring or retainer contracts? What is your average contract length and monthly churn rate?</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>[Contract type / average length in months / monthly churn % or estimate]</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>If you do not track churn formally, estimate: how many clients cancel per quarter out of your total active client base?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="10" customHeight="1">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 8  —  CLIENT EDUCATION AND RETENTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="65" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>P8 Q1 — Post-sign education
+What structured onboarding, training, or education do you provide to clients after they sign?</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>[Structured education / onboarding steps provided after sign-up]</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Include kick-off calls, welcome sequences, resource libraries, portal access, check-in cadence. 'Nothing formal' is a valid answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="65" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>P8 Q2 — At-risk management
+How do you identify and manage at-risk clients? What is your average client lifespan in months?</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>[At-risk signals / management process / average client lifespan in months]</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Name your early-warning signals: missed calls, low engagement, payment delays, complaints. Describe what action you take when you spot them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="10" customHeight="1">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>PILLAR 9  —  REGULATORY AND COMPLIANCE EXPOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="65" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>P9 Q1 — Sector
+What sector do you operate in? Select from the dropdown.</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>[Select your sector from the dropdown]</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Your sector determines which regulatory frameworks apply (CQC, MHRA, FCA, SRA, Ofsted, etc.). This is mandatory for compliance analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="65" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>P9 Q2 — Guarantees
+Do you make guarantees or promises of specific results in your marketing or contracts? Describe them exactly.</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>[Exact wording of any guarantees or specific result promises, or 'None']</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Copy the exact wording from your sales page, ads, or contract. Vague answers make compliance review impossible. 'We guarantee results' is not enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="10" customHeight="1">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
-  </ignoredErrors>
+  <mergeCells count="12">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A24:C24"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A3:B3">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A$3&gt;=23</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$A$3&gt;=18</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$A$3&lt;18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Selection" error="Please select a delivery model from the list provided." promptTitle="Delivery Model" prompt="Select the model that best describes your service delivery." type="list">
+      <formula1>"Done-for-you,Done-with-you,Self-serve,Hybrid,Mixed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Selection" error="Please select your sector from the list provided." promptTitle="Sector" prompt="Select the sector that best describes your business." type="list">
+      <formula1>"Healthcare,Aesthetics,Financial Services,Legal,Education,Coaching/Consulting,E-commerce,SaaS/Tech,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/public/CinaTech_Client_Onboarding_Template.xlsx
+++ b/public/CinaTech_Client_Onboarding_Template.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -591,13 +591,13 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Complete all 23 questions before submitting. The score below updates automatically.</t>
+          <t>Complete all 24 questions before submitting. The score below updates automatically.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="4">
-        <f>IF(B6&lt;&gt;"",IF(LEFT(B6,1)&lt;&gt;"[",1,0),0)+IF(B7&lt;&gt;"",IF(LEFT(B7,1)&lt;&gt;"[",1,0),0)+IF(B8&lt;&gt;"",IF(LEFT(B8,1)&lt;&gt;"[",1,0),0)+IF(B11&lt;&gt;"",IF(LEFT(B11,1)&lt;&gt;"[",1,0),0)+IF(B12&lt;&gt;"",IF(LEFT(B12,1)&lt;&gt;"[",1,0),0)+IF(B13&lt;&gt;"",IF(LEFT(B13,1)&lt;&gt;"[",1,0),0)+IF(B16&lt;&gt;"",IF(LEFT(B16,1)&lt;&gt;"[",1,0),0)+IF(B17&lt;&gt;"",IF(LEFT(B17,1)&lt;&gt;"[",1,0),0)+IF(B18&lt;&gt;"",IF(LEFT(B18,1)&lt;&gt;"[",1,0),0)+IF(B21&lt;&gt;"",IF(LEFT(B21,1)&lt;&gt;"[",1,0),0)+IF(B22&lt;&gt;"",IF(LEFT(B22,1)&lt;&gt;"[",1,0),0)+IF(B25&lt;&gt;"",IF(LEFT(B25,1)&lt;&gt;"[",1,0),0)+IF(B26&lt;&gt;"",IF(LEFT(B26,1)&lt;&gt;"[",1,0),0)+IF(B29&lt;&gt;"",IF(LEFT(B29,1)&lt;&gt;"[",1,0),0)+IF(B30&lt;&gt;"",IF(LEFT(B30,1)&lt;&gt;"[",1,0),0)+IF(B31&lt;&gt;"",IF(LEFT(B31,1)&lt;&gt;"[",1,0),0)+IF(B34&lt;&gt;"",IF(LEFT(B34,1)&lt;&gt;"[",1,0),0)+IF(B35&lt;&gt;"",IF(LEFT(B35,1)&lt;&gt;"[",1,0),0)+IF(B36&lt;&gt;"",IF(LEFT(B36,1)&lt;&gt;"[",1,0),0)+IF(B39&lt;&gt;"",IF(LEFT(B39,1)&lt;&gt;"[",1,0),0)+IF(B40&lt;&gt;"",IF(LEFT(B40,1)&lt;&gt;"[",1,0),0)+IF(B43&lt;&gt;"",IF(LEFT(B43,1)&lt;&gt;"[",1,0),0)+IF(B44&lt;&gt;"",IF(LEFT(B44,1)&lt;&gt;"[",1,0),0)</f>
+        <f>IF(B6&lt;&gt;"",IF(LEFT(B6,1)&lt;&gt;"[",1,0),0)+IF(B7&lt;&gt;"",IF(LEFT(B7,1)&lt;&gt;"[",1,0),0)+IF(B8&lt;&gt;"",IF(LEFT(B8,1)&lt;&gt;"[",1,0),0)+IF(B11&lt;&gt;"",IF(LEFT(B11,1)&lt;&gt;"[",1,0),0)+IF(B12&lt;&gt;"",IF(LEFT(B12,1)&lt;&gt;"[",1,0),0)+IF(B13&lt;&gt;"",IF(LEFT(B13,1)&lt;&gt;"[",1,0),0)+IF(B16&lt;&gt;"",IF(LEFT(B16,1)&lt;&gt;"[",1,0),0)+IF(B17&lt;&gt;"",IF(LEFT(B17,1)&lt;&gt;"[",1,0),0)+IF(B18&lt;&gt;"",IF(LEFT(B18,1)&lt;&gt;"[",1,0),0)+IF(B21&lt;&gt;"",IF(LEFT(B21,1)&lt;&gt;"[",1,0),0)+IF(B22&lt;&gt;"",IF(LEFT(B22,1)&lt;&gt;"[",1,0),0)+IF(B25&lt;&gt;"",IF(LEFT(B25,1)&lt;&gt;"[",1,0),0)+IF(B26&lt;&gt;"",IF(LEFT(B26,1)&lt;&gt;"[",1,0),0)+IF(B29&lt;&gt;"",IF(LEFT(B29,1)&lt;&gt;"[",1,0),0)+IF(B30&lt;&gt;"",IF(LEFT(B30,1)&lt;&gt;"[",1,0),0)+IF(B31&lt;&gt;"",IF(LEFT(B31,1)&lt;&gt;"[",1,0),0)+IF(B34&lt;&gt;"",IF(LEFT(B34,1)&lt;&gt;"[",1,0),0)+IF(B35&lt;&gt;"",IF(LEFT(B35,1)&lt;&gt;"[",1,0),0)+IF(B36&lt;&gt;"",IF(LEFT(B36,1)&lt;&gt;"[",1,0),0)+IF(B37&lt;&gt;"",IF(LEFT(B37,1)&lt;&gt;"[",1,0),0)+IF(B40&lt;&gt;"",IF(LEFT(B40,1)&lt;&gt;"[",1,0),0)+IF(B41&lt;&gt;"",IF(LEFT(B41,1)&lt;&gt;"[",1,0),0)+IF(B44&lt;&gt;"",IF(LEFT(B44,1)&lt;&gt;"[",1,0),0)+IF(B45&lt;&gt;"",IF(LEFT(B45,1)&lt;&gt;"[",1,0),0)</f>
         <v/>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -1028,125 +1028,143 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="10" customHeight="1">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="37" ht="65" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>P7 Q4 — Pricing Structure
+How is your service or product currently priced? Please include your pricing structure, any tiers or packages you offer, and how you arrived at these prices (e.g. cost-plus, value-based, competitor benchmarking).</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>[Pricing model / tier or package names and prices / rationale for pricing approach]</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Include specific price points or ranges if possible. Note whether prices are fixed or negotiated, and whether they differ by client type or volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="10" customHeight="1">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>PILLAR 8  —  CLIENT EDUCATION AND RETENTION</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="40" ht="65" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>P8 Q1 — Post-sign education
 What structured onboarding, training, or education do you provide to clients after they sign?</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>[Structured education / onboarding steps provided after sign-up]</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Include kick-off calls, welcome sequences, resource libraries, portal access, check-in cadence. 'Nothing formal' is a valid answer.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41" ht="65" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>P8 Q2 — At-risk management
 How do you identify and manage at-risk clients? What is your average client lifespan in months?</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>[At-risk signals / management process / average client lifespan in months]</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Name your early-warning signals: missed calls, low engagement, payment delays, complaints. Describe what action you take when you spot them.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="10" customHeight="1">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="42" ht="10" customHeight="1">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>PILLAR 9  —  REGULATORY AND COMPLIANCE EXPOSURE</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44" ht="65" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>P9 Q1 — Sector
 What sector do you operate in? Select from the dropdown.</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>[Select your sector from the dropdown]</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Your sector determines which regulatory frameworks apply (CQC, MHRA, FCA, SRA, Ofsted, etc.). This is mandatory for compliance analysis.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45" ht="65" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>P9 Q2 — Guarantees
 Do you make guarantees or promises of specific results in your marketing or contracts? Describe them exactly.</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>[Exact wording of any guarantees or specific result promises, or 'None']</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>Copy the exact wording from your sales page, ads, or contract. Vague answers make compliance review impossible. 'We guarantee results' is not enough.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="10" customHeight="1">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
+    <row r="46" ht="10" customHeight="1">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A24:C24"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:B3">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$A$3&gt;=23</formula>
+      <formula>$A$3&gt;=24</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>$A$3&gt;=18</formula>
@@ -1159,7 +1177,7 @@
     <dataValidation sqref="B29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Selection" error="Please select a delivery model from the list provided." promptTitle="Delivery Model" prompt="Select the model that best describes your service delivery." type="list">
       <formula1>"Done-for-you,Done-with-you,Self-serve,Hybrid,Mixed"</formula1>
     </dataValidation>
-    <dataValidation sqref="B43" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Selection" error="Please select your sector from the list provided." promptTitle="Sector" prompt="Select the sector that best describes your business." type="list">
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Selection" error="Please select your sector from the list provided." promptTitle="Sector" prompt="Select the sector that best describes your business." type="list">
       <formula1>"Healthcare,Aesthetics,Financial Services,Legal,Education,Coaching/Consulting,E-commerce,SaaS/Tech,Other"</formula1>
     </dataValidation>
   </dataValidations>
